--- a/Intersecciones/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-127870</t>
+          <t>I-341076</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-12.214583</t>
+          <t>-12.1975571</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-76.932771</t>
+          <t>-76.9423295</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Av. Central con Av. Bolivar</t>
+          <t>Calle 7 / Calle F</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-100160</t>
+          <t>I-32353</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-12.1944256</t>
+          <t>-12.2234081</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-76.9609055</t>
+          <t>-76.9597511</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Calle 1 / Calle 10</t>
+          <t>Avenida César Vallejo / Avenida Jorge Chávez</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-102578</t>
+          <t>I-224433</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -612,22 +612,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-12.2362776</t>
+          <t>-12.2381848</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-76.9202685</t>
+          <t>-76.9565869</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Calle C / Calle D</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-102585</t>
+          <t>I-224469</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,22 +664,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-12.2365303</t>
+          <t>-12.2356174</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-76.9207034</t>
+          <t>-76.9336599</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Calle 19 / Calle C</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-102587</t>
+          <t>I-224468</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-12.2363354</t>
+          <t>-12.2364017</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-76.9203679</t>
+          <t>-76.9325502</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Calle 23 / Calle C</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l-109487</t>
+          <t>I-224467</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-12.2277471</t>
+          <t>-12.2358523</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-76.9385152</t>
+          <t>-76.9338214</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pasaje 8</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -795,7 +795,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>l-109495</t>
+          <t>I-224466</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -820,22 +820,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-12.2280266</t>
+          <t>-12.2366315</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-76.9383442</t>
+          <t>-76.9327163</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida José Olaya</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>l-309645</t>
+          <t>I-224438</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-12.216937</t>
+          <t>-12.2374487</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-76.931334</t>
+          <t>-76.9579773</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Av. Central con Av. 03 de Octubre</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>l-143346</t>
+          <t>I-224437</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -924,22 +924,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-12.1974913</t>
+          <t>-12.2378787</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-76.9533568</t>
+          <t>-76.9571574</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Calle 2 / Calle A</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -951,7 +951,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>l-143712</t>
+          <t>I-224436</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -976,22 +976,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-12.1946707</t>
+          <t>-12.238469</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-76.9613307</t>
+          <t>-76.9560481</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Calle 10 / Calle 13</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>l-144158</t>
+          <t>I-224435</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1028,22 +1028,22 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-12.2249949</t>
+          <t>-12.237622</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-76.932934</t>
+          <t>-76.957636</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Avenida José Olaya / Avenida Los Alamos</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1055,7 +1055,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>l-144159</t>
+          <t>I-224434</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1080,753 +1080,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-12.2250368</t>
+          <t>-12.2371613</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-76.9330121</t>
+          <t>-76.9585433</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avenida José Olaya / Avenida Los Alamos</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>l-146533</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-12.2437682</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-76.9218021</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Calle 100 / Calle 90</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>l-127889</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-12.2174343</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-76.9373969</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>AV. BOLIVAR CON AV. LOS ALAMOS</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>l-309663</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-12.2149821</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-76.9325018</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Avenida Central</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>l-341076</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-12.1975571</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>-76.9423295</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Calle 7 / Calle F</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>l-341092</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-12.2150024</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-76.9323918</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Avenida Central</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>l-363261</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-12.2249168</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-76.9329805</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Avenida José Olaya / Avenida Los Alamos</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>l-363262</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-12.224963</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-76.93306</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Avenida José Olaya / Avenida Los Alamos</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>l-381598</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-12.2362978</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-76.9164385</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Avenida Las Lomas / Avenida Separadora Industrial</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>l-381601</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-12.2363746</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-76.9163928</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Avenida Las Lomas / Avenida Separadora Industrial</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>l-593966</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-12.2149864</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-76.9320632</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>l-593971</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-12.2149893</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-76.9323671</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>l-95623</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-12.2257721</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-76.9393716</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>l-95627</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-12.2276425</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-76.9382461</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>l-95629</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-12.2278844</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-76.9381005</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Avenida José Olaya</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
         <is>
           <t>150142</t>
         </is>

--- a/Intersecciones/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>VILLA_EL_SALVADOR</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-341076</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-12.1975571</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>150142</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VILLA_EL_SALVADOR</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-32353</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-12.2234081</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>150142</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VILLA_EL_SALVADOR</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-224433</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-12.2381848</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>150142</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VILLA_EL_SALVADOR</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-224469</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-12.2356174</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>150142</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VILLA_EL_SALVADOR</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-224468</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-12.2364017</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>150142</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VILLA_EL_SALVADOR</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-224467</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-12.2358523</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>150142</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VILLA_EL_SALVADOR</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-224466</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-12.2366315</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>150142</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VILLA_EL_SALVADOR</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-224438</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-12.2374487</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>150142</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VILLA_EL_SALVADOR</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-224437</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-12.2378787</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>150142</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VILLA_EL_SALVADOR</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-224436</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-12.238469</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>150142</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VILLA_EL_SALVADOR</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-224435</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-12.237622</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>150142</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VILLA_EL_SALVADOR</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-224434</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-12.2371613</t>
@@ -1096,11 +1036,6 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>150142</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">

--- a/Intersecciones/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,51 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>
@@ -1034,6 +1022,429 @@
         </is>
       </c>
       <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>I-93294</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-12.2308624</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-76.9228996</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Av. Guardia Republicana con Calle Vereda 11</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>I-103718</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-12.2057897</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-76.9308908</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Av. Artesanos con Calle 5</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>I-147200</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-12.2076684</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-76.9297307</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Av. Artesanos con Calle El Tudi</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>I-147205</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-12.2090076</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-76.9289375</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Av. Artesanos con Av. Cesar Vallejo</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>I-147208</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-12.2063644</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-76.9305379</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Av. Artesanos con Calle Formón</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>I-147267</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-12.2107022</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-76.9279093</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Av. Artesanos con Av. Pulidores</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>I-363207</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-12.212167</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-76.9406702</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Av. Alamos con Av. Jorge Chávez</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>I-363235</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-12.2173024</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-76.9376659</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Av. Bolívar con Av. Los Álamos</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>I-797932</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-12.214419</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-76.9328384</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Av. Central con Av. Bolívar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/Intersecciones/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
+++ b/Intersecciones/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,27 +486,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-341076</t>
+          <t>I-93294</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-12.1975571</t>
+          <t>-12.2308624</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-76.9423295</t>
+          <t>-76.9228996</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Calle 7 / Calle F</t>
+          <t>Av. Guardia Republicana con Calle Vereda 11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -533,22 +533,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-32353</t>
+          <t>I-797932</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-12.2234081</t>
+          <t>-12.214419</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-76.9597511</t>
+          <t>-76.9328384</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida César Vallejo / Avenida Jorge Chávez</t>
+          <t>Av. Central con Av. Bolívar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -580,22 +580,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-224433</t>
+          <t>I-363235</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-12.2381848</t>
+          <t>-12.2173024</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-76.9565869</t>
+          <t>-76.9376659</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Av. Bolívar con Av. Los Álamos</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-224469</t>
+          <t>I-363207</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-12.2356174</t>
+          <t>-12.212167</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-76.9336599</t>
+          <t>-76.9406702</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Av. Alamos con Av. Jorge Chávez</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -674,27 +674,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-224468</t>
+          <t>I-341076</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-12.2364017</t>
+          <t>-12.1975571</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-76.9325502</t>
+          <t>-76.9423295</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle 7 / Calle F</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-224467</t>
+          <t>I-338602</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-12.2358523</t>
+          <t>-12.1933549</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-76.9338214</t>
+          <t>-76.9552545</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Micaela Bastidas / Avenida Modelo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-224466</t>
+          <t>I-338597</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-12.2366315</t>
+          <t>-12.18867</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-76.9327163</t>
+          <t>-76.9471582</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Modelo / Calle E</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -815,22 +815,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-224438</t>
+          <t>I-338594</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-12.2374487</t>
+          <t>-12.1924407</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-76.9579773</t>
+          <t>-76.9536536</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Modelo / Calle B</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -862,22 +862,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-224437</t>
+          <t>I-32353</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-12.2378787</t>
+          <t>-12.2234081</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-76.9571574</t>
+          <t>-76.9597511</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida César Vallejo / Avenida Jorge Chávez</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -909,17 +909,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-224436</t>
+          <t>I-224469</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-12.238469</t>
+          <t>-12.2356174</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-76.9560481</t>
+          <t>-76.9336599</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-224435</t>
+          <t>I-224468</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-12.237622</t>
+          <t>-12.2364017</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-76.957636</t>
+          <t>-76.9325502</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-224434</t>
+          <t>I-224467</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-12.2371613</t>
+          <t>-12.2358523</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-76.9585433</t>
+          <t>-76.9338214</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1050,22 +1050,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-93294</t>
+          <t>I-224466</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-12.2308624</t>
+          <t>-12.2366315</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-76.9228996</t>
+          <t>-76.9327163</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Av. Guardia Republicana con Calle Vereda 11</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1097,22 +1097,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-103718</t>
+          <t>I-224438</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-12.2057897</t>
+          <t>-12.2374487</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-76.9308908</t>
+          <t>-76.9579773</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Av. Artesanos con Calle 5</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1144,22 +1144,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-147200</t>
+          <t>I-224437</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-12.2076684</t>
+          <t>-12.2378787</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-76.9297307</t>
+          <t>-76.9571574</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Av. Artesanos con Calle El Tudi</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1191,22 +1191,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-147205</t>
+          <t>I-224436</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-12.2090076</t>
+          <t>-12.238469</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-76.9289375</t>
+          <t>-76.9560481</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Av. Artesanos con Av. Cesar Vallejo</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1238,22 +1238,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-147208</t>
+          <t>I-224435</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-12.2063644</t>
+          <t>-12.237622</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-76.9305379</t>
+          <t>-76.957636</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Av. Artesanos con Calle Formón</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1285,22 +1285,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-147267</t>
+          <t>I-224434</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-12.2107022</t>
+          <t>-12.2371613</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-76.9279093</t>
+          <t>-76.9585433</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Av. Artesanos con Av. Pulidores</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1332,22 +1332,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-363207</t>
+          <t>I-224433</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-12.212167</t>
+          <t>-12.2381848</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-76.9406702</t>
+          <t>-76.9565869</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Av. Alamos con Av. Jorge Chávez</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1379,22 +1379,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-363235</t>
+          <t>I-16788</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-12.2173024</t>
+          <t>-12.2408504</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-76.9376659</t>
+          <t>-76.9115894</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Av. Bolívar con Av. Los Álamos</t>
+          <t>Avenida Lima / Calle s / n</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1426,25 +1426,213 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-797932</t>
+          <t>I-147267</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-12.214419</t>
+          <t>-12.2107022</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-76.9328384</t>
+          <t>-76.9279093</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Av. Central con Av. Bolívar</t>
+          <t>Av. Artesanos con Av. Pulidores</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>I-147208</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-12.2063644</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-76.9305379</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Av. Artesanos con Calle Formón</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>I-147205</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-12.2090076</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-76.9289375</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Av. Artesanos con Av. Cesar Vallejo</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>I-147200</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-12.2076684</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-76.9297307</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Av. Artesanos con Calle El Tudi</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>I-103718</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-12.2057897</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-76.9308908</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Av. Artesanos con Calle 5</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
